--- a/IOLCalcdata.xlsx
+++ b/IOLCalcdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C542833-AC32-4079-9050-3E95FBB3E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4367DF96-7162-4452-9334-4CB1E2387C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="150" windowWidth="20220" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="945" windowWidth="27720" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>attack01</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Surgeon</t>
   </si>
@@ -52,10 +49,6 @@
   </si>
   <si>
     <t>eye</t>
-  </si>
-  <si>
-    <t>R</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>K1</t>
@@ -101,20 +94,18 @@
   </si>
   <si>
     <t>Haigis_SE</t>
-  </si>
-  <si>
-    <t>KALA</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="180" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -180,14 +171,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -203,14 +191,56 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -518,169 +548,499 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="1" customWidth="1"/>
-    <col min="2" max="4" width="9.125" style="2" customWidth="1"/>
-    <col min="5" max="8" width="9.125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.125" style="6" customWidth="1"/>
-    <col min="10" max="12" width="9.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="9.125" style="9" customWidth="1"/>
-    <col min="15" max="16" width="9.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="9" style="16"/>
+    <col min="4" max="4" width="8.125" style="16" customWidth="1"/>
+    <col min="5" max="7" width="9" style="6"/>
+    <col min="8" max="8" width="9" style="19"/>
+    <col min="9" max="9" width="13.625" style="16" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="17" customWidth="1"/>
+    <col min="11" max="13" width="9" style="18"/>
+    <col min="14" max="14" width="9" style="15"/>
+    <col min="15" max="16" width="9" style="16"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="L1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="M1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1">
-        <v>105737</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7">
-        <v>23.33</v>
-      </c>
-      <c r="F2" s="7">
-        <v>44.25</v>
-      </c>
-      <c r="G2" s="7">
-        <v>44.75</v>
-      </c>
-      <c r="H2" s="7">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-      <c r="J2" s="10">
-        <v>5.64</v>
-      </c>
-      <c r="K2" s="10">
-        <v>-0.76900000000000002</v>
-      </c>
-      <c r="L2" s="10">
-        <v>0.23400000000000001</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0.217</v>
-      </c>
-      <c r="N2" s="9">
-        <v>21.5</v>
-      </c>
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="5"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="5"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="1"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="5"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="1"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="5"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="1"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="5"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="1"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="5"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="1"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="5"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="1"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="5"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="1"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="5"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="1"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="5"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="5"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="5"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+    </row>
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="5"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="5"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="5"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+    </row>
+    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="5"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="5"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="5"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+    </row>
+    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="5"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="5"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="5"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="5"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="5"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+    </row>
+    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="5"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+    </row>
+    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="5"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+    </row>
+    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="5"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+    </row>
+    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="5"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="5"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="5"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="5"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="5"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+    </row>
+    <row r="33" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="5"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="11"/>
+      <c r="N34" s="21"/>
+    </row>
+    <row r="35" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="11"/>
+      <c r="N35" s="21"/>
+    </row>
+    <row r="36" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="22"/>
+    </row>
+    <row r="37" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="22"/>
+    </row>
+    <row r="39" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I39" s="23"/>
+    </row>
+    <row r="40" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I40" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
